--- a/data/reporte_2026-02-23.xlsx
+++ b/data/reporte_2026-02-23.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Cruce" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,32 +426,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nro_proceso</t>
+          <t>organismo_contratante</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detalle</t>
+          <t>proveedor_adjudicado</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>tipo_proceso</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>fecha_apertura</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>en_tgn</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>monto_pagado_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>alerta</t>
         </is>
       </c>
     </row>
@@ -461,32 +498,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Contratación de UN (1) Servicio de limpieza para la intendencia del Parque Nacional Perito Moreno.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>23/02/2026 09:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407956/20260223</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -498,32 +544,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIAL PARA LA PRODUCCIÓN DE BOTAS DE COMBATE CUERO MARRÓN - AÑO 2026</t>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>23/02/2026 09:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
+          <t>MELENZANE S</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407957/20260223</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -535,32 +594,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADQUISICION DE INSUMOS DESTINADOS AL SERVICIO DE MICROBIOLOGIA DEL DEPARTAMENTO BIQUIMICA DEL HMC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>23/02/2026 09:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>Licitación Pública (Modo IV) 10/2025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407958/20260223</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -572,32 +640,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CARNES PARA LA III BRIGADA AEREA</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>ELEVAR SRL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23/02/2026 09:00 Hrs.</t>
+          <t>30-71439091-7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>$1.164.000,00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -609,32 +698,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADQUISICION DE ALIMENTOS PARA CANES</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>23/02/2026 09:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>Licitación Pública 431/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407960/20260223</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -646,32 +744,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prestación del servicio de preparación de superficie mediante método de arenado y pintado.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>23/02/2026 09:30 Hrs.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0029-LPU25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407961/20260223</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
         </is>
       </c>
     </row>
@@ -683,32 +790,830 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Servicio para la recepción, elaboración y distribución de alimentos.</t>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30-70876378-7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPRAR  63-0063-LPU25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407962/20260223</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_completo</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2407956</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407956/20260223</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Volver Contrataciones Tercera sección Tercera Preadjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso MINISTERIO PÚBLICO DE LA DEFENSA - 
+DEFENSORÍA GENERAL DE LA NACIÓN Licitación Pública 49/2025 EXPEDIENTE Nº: 64251/2025 OBJETO: Adquisición de insumos para impresoras OKI instaladas en dependencias del Ministerio Público de la Defensa. LUGAR Y HORARIO DE CONSULTA DEL EXPEDIENTE: Departamento de Compras y Contrataciones - de lunes a viernes de 9.30 a 16:00 hs. – Tacuarí 139/47 P</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA -</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2407957</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407957/20260223</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MELENZANE S</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Volver Contrataciones Tercera sección Tercera Preadjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso MINISTERIO PÚBLICO DE LA DEFENSA - 
+DEFENSORÍA GENERAL DE LA NACIÓN Licitación Pública 59/2025 EXPEDIENTE: EX-2025-64092- -MPD-DGAD#MPD OBJETO: Adquisición de elementos de seguridad e higiene para dependencias varias del Ministerio Público de la Defensa. LUGAR Y HORARIO DE CONSULTA DEL EXPEDIENTE: Departamento de Compras y Contrataciones- de lunes a viernes de 9.30 a 16:00 hs. –</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 10/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2407958</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407958/20260223</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E. Licitación Pública (Modo IV) 10/2025 SOLPED N° 10.000.071. “Mantenimiento Correctivo en el Edificio Operativo, Torre de Control, Planta Transmisora, Edificio Radar y Plan de Vuelo en el Aeropuerto de Córdoba” En cumplimiento del Reglamento de Compras y Contrataciones de EANA y de acuerdo al punto xvi) del Artículo XII, se publica el result</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2407959</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407959/20260223</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ELEVAR SRL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30-71439091-7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>$1.164.000,00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - 
+DIRECCIÓN REGIONAL ADUANERA CENTRAL Contratación Directa 01/26 Expediente Nº: EX-2026-00012912- -ARCA-SECFDVAFCE#SDGOAI Objeto de la contratación: Servicio de mantenimiento Ascensor Edificio Sede Aduana Córdoba Adjudicatario ELEVAR SRL CUIT N.º 30-71439091-7 Total Adjudicado: $ 1.164.000,00 La Dirección Regional Aduanera Central informa </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 431/2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2407960</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407960/20260223</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ARMADA ARGENTINA Licitación Pública 431/2025 UOC: 38/5 - División de Compras - Arsenal Aereonaval Comandante Espora Ejercicio: 2025 Clase: Única Nacional Modalidad: Orden de compra abierta Expediente N°: EX-2025-115587397- -APN-DAA#ARA Objeto: Necesarios contar con dichos repuestos para poner en servicio Aeronave AS555, al que se aplicará este Pliego de Bases y Condiciones Particul</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0029-LPU25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2407961</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407961/20260223</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL Licitación Pública PROCESO COMPR.AR 63-0029-LPU25 PROCESO COMPR.AR N° 63-0029-LPU25 Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: SIN MODALIDAD N° de Expediente Electrónico: EX-2025-54939691- -ANSES-DC#ANSES Objeto: Servicio de control de plagas y un servicio de limpieza de tanques de agua con su análisis físico-quími</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>Licitación Pública PROCESO COMPRAR  63-0063-LPU25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>2407962</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407962/20260223</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>30-70876378-7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volver Contrataciones Tercera sección Tercera Adjudicaciones Detalle | | Ver páginas publicadas Ver texto del aviso ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL Licitación Pública PROCESO COMPRAR 63-0063-LPU25 Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: Sin modalidad. Nº de Expediente: EX-2025-85188315-ANSES-DC#ANSES Objeto: Suministro y distribución de bidones de agua potable con provisión e instalación de dispensadores de agua frío/calor compatible, en comodato, incluido </t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>es_adjudicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0001/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - COMBUSTIBLES, LUBRICANTES Y ACEITES</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2407926</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407926/20260223</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0003/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - COMBUSTIBLES, LUBRICANTES Y ACEITES</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2407927</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407927/20260223</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0051/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - COMPONENTES Y ACCESORIOS DE AERONAVES</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2407928</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407928/20260223</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SANIDAD Y CALIDAD AGROALIMENTARIA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0002/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2407929</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407929/20260223</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FABRICACIONES MILITARES SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública LPU-2026-SC-007</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2407930</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407930/20260223</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FABRICACIONES MILITARES SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública LPU-2026-SC-008</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2407931</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407931/20260223</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AGUA Y SANEAMIENTOS ARGENTINOS S.A.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 64785/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2407932</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407932/20260223</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
@@ -720,32 +1625,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Servicio de locación, mantenimiento y gestión de impresiones digitales (Impresión y Fotocopiado)</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>COMISIÓN NACIONAL DE ENERGÍA ATÓMICA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>Licitación Pública 54/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>2407933</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407933/20260223</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
@@ -757,32 +1670,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Servicio de Fotocopiadora para la ESCUELA DE AVAICION MILITAR</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>2407934</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407934/20260223</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
@@ -794,32 +1715,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PROVISIÓN DE CARTAS ELECTRÓNICAS PERTENECIENTES AL BUQUE ESCUELA FRAGATA A.R.A. "LIBERTAD".</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23/02/2026 10:00 Hrs.</t>
+          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>2407935</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407935/20260223</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
@@ -831,32 +1760,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Licitación Pública 16/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>2407936</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407936/20260223</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
@@ -868,32 +1805,850 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ARMADA ARGENTINA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Licitación Pública 0021/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Scraper Comprar.gob.ar</t>
+          <t>2407937</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407937/20260223</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0022/2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2407938</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407938/20260223</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTA COMPLEJIDAD CUENCA ALTA DR. NÉSTOR CARLOS KIRCHNER (S.A.M.I.C.)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Licitación Pública 007/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2407939</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407939/20260223</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BUENOS AIRES - FACULTAD DE ODONTOLOGÍA - DIRECCIÓN DE COMPRAS Y LICITACIONES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Obra Pública – Licitación Pública 01-26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2407940</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407940/20260223</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE ENTRE RÍOS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licitación Pública 03/2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2407941</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407941/20260223</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL MENDOZA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2407942</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407942/20260223</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0049/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2407943</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407943/20260223</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0054/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2407944</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407944/20260223</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0058/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2407945</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407945/20260223</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GENDARMERÍA NACIONAL ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0067/2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2407946</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407946/20260223</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BANCO CENTRAL DE LA REPÚBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Licitación Pública 06/26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2407947</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407947/20260223</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HONORABLE SENADO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Licitación Pública 1/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2407948</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407948/20260223</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CASA DE MONEDA S.A.U.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Licitación Pública 974</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2407949</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407949/20260223</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN DE COMPRAS, INFRAESTRUCTURA Y LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2407950</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407950/20260223</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AGENCIA DE PUBLICIDAD DEL ESTADO S.A.U.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Contratación Directa por Compulsa Abreviada  002/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2407951</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407951/20260223</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTA COMPLEJIDAD CUENCA ALTA DR. NÉSTOR CARLOS KIRCHNER (S.A.M.I.C.)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licitación Pública 009/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2407952</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407952/20260223</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0015/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - CONCESIONES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2407953</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407953/20260223</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL JUNÍN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2407954</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407954/20260223</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JEFATURA DE GABINETE DE MINISTROS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Licitación Pública 4/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LOCACIONES - VARIOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2407955</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2407955/20260223</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
         </is>
       </c>
     </row>
